--- a/Listing/IFD04D.xlsx
+++ b/Listing/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
   <si>
     <t/>
   </si>
@@ -52,6 +52,15 @@
     <t>6</t>
   </si>
   <si>
+    <t>20141070</t>
+  </si>
+  <si>
+    <t>KOBE MI CH/OIL LV.15</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20062365</t>
   </si>
   <si>
@@ -229,9 +238,6 @@
     <t>WOW SPAGHETI BOLOG76</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20135312</t>
   </si>
   <si>
@@ -268,21 +274,15 @@
     <t>INDOMIE AYAM BWG 5S</t>
   </si>
   <si>
-    <t>20103442</t>
-  </si>
-  <si>
-    <t>ABC MI GRNG SP PDS80</t>
+    <t>10007606</t>
+  </si>
+  <si>
+    <t>ABC MIE GULAI PDS.70</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>10007606</t>
-  </si>
-  <si>
-    <t>ABC MIE GULAI PDS.70</t>
-  </si>
-  <si>
     <t>10003435</t>
   </si>
   <si>
@@ -505,21 +505,15 @@
     <t>INDOMIE GRG RNDNG120</t>
   </si>
   <si>
-    <t>20073671</t>
-  </si>
-  <si>
-    <t>BD MIE URAI PPH 140G</t>
+    <t>20085013</t>
+  </si>
+  <si>
+    <t>BD MIE URAI ORG 140G</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20085013</t>
-  </si>
-  <si>
-    <t>BD MIE URAI ORG 140G</t>
-  </si>
-  <si>
     <t>10000507</t>
   </si>
   <si>
@@ -541,15 +535,36 @@
     <t>3AYAM MIE TLR KNG200</t>
   </si>
   <si>
+    <t>20043409</t>
+  </si>
+  <si>
+    <t>IDM BIHUN BERAS 220G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20034699</t>
+  </si>
+  <si>
+    <t>BIHUN JAGUNG 320G</t>
+  </si>
+  <si>
+    <t>20140909</t>
+  </si>
+  <si>
+    <t>B.FARM TERI KB 60G</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20020770</t>
   </si>
   <si>
     <t>MERBABU KR.BAWANG200</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
@@ -601,6 +616,12 @@
     <t>PALDO HOT&amp;SPICY 120</t>
   </si>
   <si>
+    <t>20141198</t>
+  </si>
+  <si>
+    <t>WONHAE TPOKI CARB 80</t>
+  </si>
+  <si>
     <t>20127764</t>
   </si>
   <si>
@@ -625,7 +646,7 @@
     <t>20128247</t>
   </si>
   <si>
-    <t>WNHAE FRIED ROSE 120</t>
+    <t>WNHAE FRIED ROSE 97G</t>
   </si>
   <si>
     <t>20117989</t>
@@ -634,12 +655,6 @@
     <t>M/S TOPOKKI ORI 132G</t>
   </si>
   <si>
-    <t>20116882</t>
-  </si>
-  <si>
-    <t>M/S TOPOKKI SPCY 132</t>
-  </si>
-  <si>
     <t>20138114</t>
   </si>
   <si>
@@ -751,6 +766,18 @@
     <t>NISSIN HOT CARBO 120</t>
   </si>
   <si>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMNYES TKYO CHKN 84G</t>
+  </si>
+  <si>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMNYES HKTA CHKN 88G</t>
+  </si>
+  <si>
     <t>20039494</t>
   </si>
   <si>
@@ -772,27 +799,18 @@
     <t>BIHUNKU SOTO SPS 55G</t>
   </si>
   <si>
+    <t>20141374</t>
+  </si>
+  <si>
+    <t>BIHUNKU BASO SAPI 50</t>
+  </si>
+  <si>
     <t>10000653</t>
   </si>
   <si>
     <t>SP.BHUN INST KUAH 51</t>
   </si>
   <si>
-    <t>20043409</t>
-  </si>
-  <si>
-    <t>IDM BIHUN BERAS 220G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20034699</t>
-  </si>
-  <si>
-    <t>BIHUN JAGUNG 320G</t>
-  </si>
-  <si>
     <t>10037027</t>
   </si>
   <si>
@@ -830,6 +848,18 @@
   </si>
   <si>
     <t>SUPER BUBUR KARI 46G</t>
+  </si>
+  <si>
+    <t>20140905</t>
+  </si>
+  <si>
+    <t>NASINDO NASI GR. 85G</t>
+  </si>
+  <si>
+    <t>20140904</t>
+  </si>
+  <si>
+    <t>NASINDO SOTO 65G</t>
   </si>
   <si>
     <t>20045610</t>
@@ -1438,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1540,73 +1570,73 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1620,41 +1650,41 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1663,18 +1693,18 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1683,18 +1713,18 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1703,158 +1733,158 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1863,18 +1893,18 @@
         <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1883,18 +1913,18 @@
         <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1903,18 +1933,18 @@
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1923,18 +1953,18 @@
         <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1943,38 +1973,38 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1983,18 +2013,18 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2003,18 +2033,18 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2023,18 +2053,18 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2043,18 +2073,18 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2063,30 +2093,30 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2100,13 +2130,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2120,13 +2150,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2140,13 +2170,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2160,10 +2190,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -2180,10 +2210,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2200,10 +2230,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2220,33 +2250,33 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2260,7 +2290,7 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>5</v>
@@ -2280,10 +2310,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2300,7 +2330,7 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>9</v>
@@ -2343,7 +2373,7 @@
         <v>98</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2443,7 +2473,7 @@
         <v>109</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2483,7 +2513,7 @@
         <v>109</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2563,7 +2593,7 @@
         <v>122</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2603,7 +2633,7 @@
         <v>122</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2663,7 +2693,7 @@
         <v>122</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -2723,7 +2753,7 @@
         <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2763,7 +2793,7 @@
         <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2823,7 +2853,7 @@
         <v>140</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2863,7 +2893,7 @@
         <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2903,7 +2933,7 @@
         <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -2943,10 +2973,10 @@
         <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,18 +2993,18 @@
         <v>166</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2983,10 +3013,10 @@
         <v>166</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3003,7 +3033,7 @@
         <v>166</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -3023,50 +3053,50 @@
         <v>166</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>179</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3080,13 +3110,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3100,33 +3130,33 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>187</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="E84" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3140,73 +3170,73 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3220,13 +3250,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3240,13 +3270,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3260,93 +3290,93 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3360,13 +3390,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3380,73 +3410,73 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3460,13 +3490,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3480,93 +3510,93 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3580,13 +3610,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3600,73 +3630,73 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3680,13 +3710,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3700,13 +3730,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,13 +3750,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3740,13 +3770,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3760,13 +3790,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3780,13 +3810,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3800,70 +3830,70 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3880,13 +3910,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3900,113 +3930,113 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4020,13 +4050,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4040,13 +4070,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4060,190 +4090,190 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4260,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4280,10 +4310,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4291,19 +4321,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4311,19 +4341,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4331,19 +4361,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4351,19 +4381,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4371,16 +4401,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>4</v>
@@ -4391,19 +4421,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4411,19 +4441,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4431,19 +4461,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4451,102 +4481,202 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E155" s="1" t="s">
+      <c r="B156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F155" s="1" t="s">
-        <v>16</v>
+      <c r="F160" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
